--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/Teaching/psyteachR/mvls_lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D7FE63-DD6E-4767-9376-6A8B5F94FB5C}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D90637A-78D5-4520-A1BB-7CA9BBDBC6B7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,7 +806,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" customWidth="1"/>
+    <col min="2" max="2" width="54.5703125" customWidth="1"/>
     <col min="3" max="3" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>

--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/Teaching/psyteachR/mvls_lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0E40E2-7291-C84E-88CF-F6786D0B1554}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{421F3126-ECCB-4980-8777-C28D3C2DC144}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -462,13 +462,19 @@
   </si>
   <si>
     <t>https://orcid.org/0000-0002-7789-1185</t>
+  </si>
+  <si>
+    <t>Leah Martin</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-9284-5518</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,15 +814,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.2890625" customWidth="1"/>
-    <col min="2" max="2" width="54.61328125" customWidth="1"/>
-    <col min="3" max="3" width="38.47265625" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="54.5703125" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -827,7 +833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -838,7 +844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -849,7 +855,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -860,7 +866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -871,7 +877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -882,7 +888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -893,7 +899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -904,7 +910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -915,7 +921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -926,7 +932,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -937,7 +943,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -948,7 +954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -959,7 +965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -970,7 +976,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -981,7 +987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -992,7 +998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -1047,7 +1053,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -1091,7 +1097,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1124,7 +1130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -1135,7 +1141,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -1157,7 +1163,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -1190,7 +1196,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1245,7 +1251,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1267,7 +1273,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -1300,7 +1306,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -1344,7 +1350,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>107</v>
       </c>
@@ -1355,7 +1361,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -1366,7 +1372,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -1377,7 +1383,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>114</v>
       </c>
@@ -1388,7 +1394,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -1399,7 +1405,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -1410,7 +1416,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>120</v>
       </c>
@@ -1421,7 +1427,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>122</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -1443,7 +1449,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>126</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -1465,7 +1471,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>132</v>
       </c>
@@ -1487,7 +1493,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -1498,7 +1504,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>136</v>
       </c>
@@ -1509,7 +1515,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>138</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>140</v>
       </c>
@@ -1529,6 +1535,17 @@
       </c>
       <c r="C65" s="1" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1594,6 +1611,7 @@
     <hyperlink ref="C10" r:id="rId56" xr:uid="{708A4E17-0586-427D-B106-9DB06F0F1341}"/>
     <hyperlink ref="C64" r:id="rId57" xr:uid="{418027A3-A711-41F9-A5A7-CEEDCA43C269}"/>
     <hyperlink ref="C65" r:id="rId58" xr:uid="{2A5635ED-DF81-EA4B-8D6E-86E01201A208}"/>
+    <hyperlink ref="C66" r:id="rId59" xr:uid="{1D8E51E0-BCC9-4309-B1E7-DFBED221BB48}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
